--- a/data/worldcup_0624_0622update.xlsx
+++ b/data/worldcup_0624_0622update.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -481,34 +481,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+          <t>Portugal vs Uzbekistan: predictions, best bets, stats and odds</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 13</t>
+          <t>2 hours ago</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+          <t>https://www.squawka.com/en/news/world-cup/portugal-vs-uzbekistan-predictions-tips/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -518,474 +522,703 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sun Jun 21 2026 15:</t>
+          <t>Sun, 21 Jun 2026 13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sun Jun 21 2026 15:</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>卡纳瓦罗：C罗和梅西一样一直是最佳之一，葡萄牙的阵容星光熠熠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>zhibo8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-22 15:55:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e9cae7ef0native.htm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-06-21T18:22:43</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
 The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-06-21T17:04:43</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-06-21T16:35:30</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
 The 2026 FIFA World Cup has completely ta</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-06-21T16:11:53</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>武磊：我感觉葡萄牙今年想要拿世界杯冠军还是挺有难度的</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-06-21 23:26</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955601.html</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>世体：葡萄牙世界杯开局低迷，C罗因队内地位引发争议</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-06-21 13:41</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5954496.html</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Golden Boot: World Cup 2026 top goalscorers</t>
+          <t>武磊：我感觉葡萄牙今年想要拿世界杯冠军还是挺有难度的</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thu, 18 Jun 2026 08</t>
+          <t>2026-06-21 23:26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/golden-boot-world-cup-2026-top-goalscorers-winner</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Who is winning the battle to be top scorer at the World Cup? Live and updated throughout the tournament  All-time World Cup goalscorers  The Golden Bo</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955601.html</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Iran’s Beiranvand denies 10-man Belgium in World Cup draw as Nathan Ngoy sees red</t>
+          <t>世体：葡萄牙世界杯开局低迷，C罗因队内地位引发争议</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 21</t>
+          <t>2026-06-21 13:41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/belgium-iran-world-cup-group-g-match-report</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>There was simply no debate over the moment of the match and it is one that Iran will cherish, even more so if they are to progress to the World Cup kn</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5954496.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
+          <t>Uzbekistan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 04</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
+          <t>https://kickoff.guide/blog/uzbekistan-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
+          <t>A team profile of Uzbekistan, who reached a first-ever FIFA World Cup: 50th in the FIFA ranking, coached by Italy's World Cup-winning captain Fabio Ca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Past and present World Cups collide as Beiranvand first gives Iran inspiration, then hope</t>
+          <t>Portugal at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Mon, 22 Jun 2026 02</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-iran-goalkeeper-alireza-beiranvand</t>
+          <t>https://kickoff.guide/blog/portugal-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">The goalkeeper’s 59th-minute save left mouths agape but it’s not the first time he has created an indelible moment for the team  As they prepared for </t>
+          <t>A team profile of Portugal at the FIFA World Cup 2026: 5th in the FIFA ranking, 9th appearance and seventh in a row, Roberto Martinez's tactics, Crist</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>World Cup 2026: Can Lionel Messi and Cristiano Ronaldo finally meet on biggest stage?</t>
+          <t>Golden Boot: World Cup 2026 top goalscorers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-22T06:43:30</t>
+          <t>Thu, 18 Jun 2026 08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48972466/world-cup-2026-lionel-messi-cristiano-ronaldo-showdown-knockouts-argentina-portugal</t>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/golden-boot-world-cup-2026-top-goalscorers-winner</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>In a sixth World Cup for Lionel Messi and Cristiano Ronaldo, could the pair finally face each other in the tournament?</t>
+          <t>Who is winning the battle to be top scorer at the World Cup? Live and updated throughout the tournament  All-time World Cup goalscorers  The Golden Bo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lamine Yamal shows why this could be his World Cup</t>
+          <t>Iran’s Beiranvand denies 10-man Belgium in World Cup draw as Nathan Ngoy sees red</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-21T19:27:01</t>
+          <t>Sun, 21 Jun 2026 21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/belgium-iran-world-cup-group-g-match-report</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
+          <t>There was simply no debate over the moment of the match and it is one that Iran will cherish, even more so if they are to progress to the World Cup kn</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>The World Cup records that look set to be broken</t>
+          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-21T13:55:05</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Past and present World Cups collide as Beiranvand first gives Iran inspiration, then hope</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 02</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-iran-goalkeeper-alireza-beiranvand</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The goalkeeper’s 59th-minute save left mouths agape but it’s not the first time he has created an indelible moment for the team  As they prepared for </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Can Lionel Messi and Cristiano Ronaldo finally meet on biggest stage?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-22T06:43:30</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/48972466/world-cup-2026-lionel-messi-cristiano-ronaldo-showdown-knockouts-argentina-portugal</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>In a sixth World Cup for Lionel Messi and Cristiano Ronaldo, could the pair finally face each other in the tournament?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Lamine Yamal shows why this could be his World Cup</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-21T19:27:01</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cj0gy46d5vro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'He's the main man!' - Rooney on Lamine Yamal  Lamine Yamal was the story before kick-off and is dominating conversation long after the final whistle </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Most FIFA World Cup Appearances by a Player</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2026-06-20T19:39:34</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-world-cup-appearances-by-a-player/</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Here are the players who have combined longevity and excellence to record the most men’s FIFA World Cup appearances of all time.
 Lionel Messi: Argent</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Most Red Cards in World Cup History: Players, Teams and Incidents That Made History</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2026-06-20T19:21:25</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-red-cards-in-world-cup-history/</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">From Zinedine Zidane’s headbutt to Wayne Rooney’s stamp, discover which players and teams have received the most red cards in FIFA World Cup history.
 </t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>The Oldest Players in World Cup History</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2026-06-20T19:09:14</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/oldest-players-in-world-cup-history/</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Age is just a number for some footballers. Some even play the game on the grandest stage of all just before the end of their career. Here, we chart th</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>FIFA World Cup Hat-Tricks: The Facts</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-06-19T00:28:32</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/world-cup-hat-tricks-fifa/</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>There have been 56 hat-tricks scored in men’s FIFA World Cup finals tournaments. We give a rundown of the best facts about World Cup hat-tricks, as we</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:38</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956424</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombia at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/colombia-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A team profile of Colombia (Los Cafeteros) at the FIFA World Cup 2026: 13th in the FIFA ranking, 7th appearance, best result the 2014 quarter-finals, </t>
         </is>
       </c>
     </row>
@@ -995,6 +1228,743 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Why the debate surrounding Jude Bellingham for England remains ahead of Ghana game</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/football/news/12040/13555646/world-cup-2026-jude-bellinghams-brilliance-against-croatia-ends-no-10-discussion-for-england-ahead-of-ghana-game</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sky Sports News' Rob Dorsett analyses Jude Bellingham's performance during England's 4-2 win against Croatia and explains why the debate surrounding t</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>England vs Ghana: predictions, best bets, stats and odds</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8 minutes ago</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-predictions-betting-tips/</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>England vs Ghana team news and predicted lineups</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>44 minutes ago</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-team-news-predicted-lineups/</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>England will look to seal their place in the knockout stages when they face Ghana in Group L at the 2026 World Cup on Tuesday. Kick-off is scheduled f</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saka trains with England squad before Ghana match</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:13:38</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c8e21d5w0pjo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bukayo Saka (right) trained with the England squad on Sunday  Bukayo Saka has trained with the England squad to provide a fitness boost to Thomas Tuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>官方：马宁担任英格兰vs加纳第四官员，周飞担任候补助理裁判</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953123.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>England v Ghana: Live stream, team news, tickets and more</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-18T07:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/england-ghana-preview-live-stream-team-news-tickets</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>This is a modal window.
+Europe and Africa go head-to-head at Boston Stadium when England and Ghana meet in their second Group L fixture.
+Tuesday, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>From Times Square to England squad: Trevoh Chalobah realises World Cup dream</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/from-times-square-to-england-squad-trevoh-chalobah-realises-world-cup-dream</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Chelsea defender has mad scramble for boots and cuts short holiday after belatedly receiving the message of a lifetime from Thomas Tuchel  T revoh Cha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Thomas Partey in spotlight as he faces England and former Arsenal teammates after rape charges</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 11</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/thomas-partey-england-ghana-handshake</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ghana midfielder has denied all accusations as he prepares to begin his World Cup campaign in Boston on Tuesday  T he Football Association has remaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sun Jun 21 2026 15:</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>skysports</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fri, 19 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>England's 2026 World Cup squad: All 26 players picked by Thomas Tuchel and why</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-22T06:26:25</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/48823863/england-2026-world-cup-squad-26-players-picked-thomas-tuchel-why</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ESPN takes a look at every player named in the England squad for the 2026 World Cup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tuchel not afraid to shout at players - Watkins</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-21T22:04:05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cjegy048847o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Thomas Tuchel has been in charge of England since January 2025  Ollie Watkins has said Thomas Tuchel is "not afraid" to shout at England players as th</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>England's Ollie Watkins on his World Cup role: 'It can be better to be a substitute than to start'</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-21T20:56:23</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49137379/england-ollie-watkins-world-cup-role-better-substitute-start</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>England striker Ollie Watkins has said he thinks his World Cup moment could be just around the corner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>The World Cup records that look set to be broken</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-21T13:55:05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cpv3kkv4z4mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Lionel Messi has appeared at six World Cups, scoring 16 goals  The 2026 World Cup may only be 10 days old but the tournament has already rewritten foo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>England at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/england-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A team profile of England (Three Lions) at the FIFA World Cup 2026: 4th in the FIFA ranking, 17th appearance, one title in 1966, Thomas Tuchel's tacti</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>邮报：皮克福德为妻子准备纪念日惊喜</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:40</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955719.html</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bukayo Saka returns to England training after individual session on Saturday</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:33:24</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/49137642/bukayo-saka-returns-england-training-individual-session-saturday</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bukayo Saka trained on Sunday ahead of England's World Cup clash with Ghana on Tuesday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>丹-伯恩：贝林厄姆能够奠定基调，他有能给你带来能量的特质</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953477.html</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:38</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956424</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>New Zealand vs Egypt FIFA World Cup 2026 Preview: Everything you need to know</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>goal_pw</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-21T10:14:27</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/en/news/new-zealand-egypt-world-cup-preview/blt1ef9c540246b6832</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GOAL brings you everything you need to know about New Zealand vs Egypt at the 2026 FIFA World Cup.
+New Zealand vs Egypt will kick-off on 21 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1038,102 +2008,206 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>World Cup 2026: Why the debate surrounding Jude Bellingham for England remains ahead of Ghana game</t>
+          <t>克罗地亚国家队队长卢卡·莫德里奇将在对阵巴拿马的...</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>skysports</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 14</t>
+          <t>2026-06-21 22:58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/football/news/12040/13555646/world-cup-2026-jude-bellinghams-brilliance-against-croatia-ends-no-10-discussion-for-england-ahead-of-ghana-game</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Sky Sports News' Rob Dorsett analyses Jude Bellingham's performance during England's 4-2 win against Croatia and explains why the debate surrounding t</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955540.html</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Saka trains with England squad before Ghana match</t>
+          <t>官方：加蓬裁判阿乔将执法世界杯巴拿马vs克罗地亚</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-22T00:13:38</t>
+          <t>2026-06-21 01:49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c8e21d5w0pjo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Bukayo Saka (right) trained with the England squad on Sunday  Bukayo Saka has trained with the England squad to provide a fitness boost to Thomas Tuch</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953239.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方：马宁担任英格兰vs加纳第四官员，周飞担任候补助理裁判</t>
+          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-21 00:30</t>
+          <t>Fri, 19 Jun 2026 10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953123.html</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>England vs Ghana: predictions, best bets, stats and odds</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8 minutes ago</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-predictions-betting-tips/</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>England vs Ghana team news and predicted lineups</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>44 minutes ago</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/england-vs-ghana-team-news-predicted-lineups/</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>England will look to seal their place in the knockout stages when they face Ghana in Group L at the 2026 World Cup on Tuesday. Kick-off is scheduled f</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saka trains with England squad before Ghana match</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-22T00:13:38</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c8e21d5w0pjo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bukayo Saka (right) trained with the England squad on Sunday  Bukayo Saka has trained with the England squad to provide a fitness boost to Thomas Tuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>克罗地亚前锋穆萨：能在熟悉的达拉斯打入世界杯首球很不可思议</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-20 01:56</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5950333.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>England v Ghana: Live stream, team news, tickets and more</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-06-18T07:00:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/england-ghana-preview-live-stream-team-news-tickets</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>This is a modal window.
 Europe and Africa go head-to-head at Boston Stadium when England and Ghana meet in their second Group L fixture.
@@ -1141,273 +2215,152 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>From Times Square to England squad: Trevoh Chalobah realises World Cup dream</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 18</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/from-times-square-to-england-squad-trevoh-chalobah-realises-world-cup-dream</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Chelsea defender has mad scramble for boots and cuts short holiday after belatedly receiving the message of a lifetime from Thomas Tuchel  T revoh Cha</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 13</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Thomas Partey in spotlight as he faces England and former Arsenal teammates after rape charges</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 11</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/thomas-partey-england-ghana-handshake</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ghana midfielder has denied all accusations as he prepares to begin his World Cup campaign in Boston on Tuesday  T he Football Association has remaine</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>England offer rare peek behind the curtain with no place to hide under Tuchel</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/england-world-cup-training-intensity-peek-behind-curtain-thomas-tuchel</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">There was more insight at the World Cup training base than usual with intensity on the rise under Thomas Tuchel  T he tall hooded figure kept barking </t>
-        </is>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+          <t>Panama at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sun Jun 21 2026 15:</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+          <t>https://kickoff.guide/blog/panama-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+          <t xml:space="preserve">A team profile of Panama (La Marea Roja) at the FIFA World Cup 2026: 33rd in the FIFA ranking, 2nd appearance, Thomas Christiansen's tactics, players </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
+          <t>Croatia at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>skysports</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 14</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
+          <t>https://kickoff.guide/blog/croatia-world-cup-2026-guide</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
+          <t>A team profile of Croatia (Vatreni) at the FIFA World Cup 2026: 11th in the FIFA ranking, 7th appearance, 2018 runners-up, Zlatko Dalic's tactics, Luk</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+          <t>Adalberto Carrasquilla Injury: Could be available Tuesday</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Fri, 19 Jun 2026 10</t>
-        </is>
-      </c>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+          <t>https://www.rotowire.com/soccer/headlines/adalberto-carrasquilla-injury-could-be-available-tuesday-520478</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+          <t>Written by RotoWire Staff
+Carrasquilla (groin) returned to the training pitch Sunday but continues to train partially ahead of Tuesday's clash agains</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>England's 2026 World Cup squad: All 26 players picked by Thomas Tuchel and why</t>
+          <t>苏契奇：适应国米对我不是问题；很难达到莫德里奇的高度</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-22T06:26:25</t>
+          <t>2026-06-22 02:49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48823863/england-2026-world-cup-squad-26-players-picked-thomas-tuchel-why</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ESPN takes a look at every player named in the England squad for the 2026 World Cup.</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955931.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tuchel not afraid to shout at players - Watkins</t>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-21T22:04:05</t>
+          <t>6 days ago</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cjegy048847o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has been in charge of England since January 2025  Ollie Watkins has said Thomas Tuchel is "not afraid" to shout at England players as th</t>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>England's Ollie Watkins on his World Cup role: 'It can be better to be a substitute than to start'</t>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>dongqiudi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-21T20:56:23</t>
+          <t>2026-06-22 08:38</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49137379/england-ollie-watkins-world-cup-role-better-substitute-start</t>
+          <t>https://www.dongqiudi.com/article/5956424</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>England striker Ollie Watkins has said he thinks his World Cup moment could be just around the corner.</t>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
         </is>
       </c>
     </row>
@@ -1441,320 +2394,80 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>邮报：皮克福德为妻子准备纪念日惊喜</t>
+          <t>New Zealand vs Egypt FIFA World Cup 2026 Preview: Everything you need to know</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>goal_pw</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-22 00:40</t>
+          <t>2026-06-21T10:14:27</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955719.html</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>https://www.goal.com/en/news/new-zealand-egypt-world-cup-preview/blt1ef9c540246b6832</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GOAL brings you everything you need to know about New Zealand vs Egypt at the 2026 FIFA World Cup.
+New Zealand vs Egypt will kick-off on 21 June 2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bukayo Saka returns to England training after individual session on Saturday</t>
+          <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-21T21:33:24</t>
+          <t>2026-06-20T16:24:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49137642/bukayo-saka-returns-england-training-individual-session-saturday</t>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bukayo Saka trained on Sunday ahead of England's World Cup clash with Ghana on Tuesday.</t>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>丹-伯恩：贝林厄姆能够奠定基调，他有能给你带来能量的特质</t>
+          <t>Ghana at the World Cup 2026: Team Guide — History, Style, Players &amp; Group L</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-06-21 05:22</t>
-        </is>
-      </c>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953477.html</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>摘要</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>克罗地亚国家队队长卢卡·莫德里奇将在对阵巴拿马的...</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-21 22:58</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955540.html</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>官方：加蓬裁判阿乔将执法世界杯巴拿马vs克罗地亚</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-21 01:49</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5953239.html</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fri, 19 Jun 2026 10</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Saka trains with England squad before Ghana match</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-06-22T00:13:38</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/c8e21d5w0pjo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bukayo Saka (right) trained with the England squad on Sunday  Bukayo Saka has trained with the England squad to provide a fitness boost to Thomas Tuch</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>克罗地亚前锋穆萨：能在熟悉的达拉斯打入世界杯首球很不可思议</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-20 01:56</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5950333.html</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>England v Ghana: Live stream, team news, tickets and more</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-18T07:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/england-ghana-preview-live-stream-team-news-tickets</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>This is a modal window.
-Europe and Africa go head-to-head at Boston Stadium when England and Ghana meet in their second Group L fixture.
-Tuesday, 23</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Adalberto Carrasquilla Injury: Could be available Tuesday</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>rotowire</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.rotowire.com/soccer/headlines/adalberto-carrasquilla-injury-could-be-available-tuesday-520478</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Written by RotoWire Staff
-Carrasquilla (groin) returned to the training pitch Sunday but continues to train partially ahead of Tuesday's clash agains</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>苏契奇：适应国米对我不是问题；很难达到莫德里奇的高度</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-06-22 02:49</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955931.html</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>https://kickoff.guide/blog/ghana-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A team profile of Ghana (Black Stars) at the FIFA World Cup 2026: 74th in the FIFA ranking, 5th appearance, best result the 2010 quarter-finals, Otto </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1767,7 +2480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1987,6 +2700,216 @@
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Portugal vs Uzbekistan: predictions, best bets, stats and odds</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2 hours ago</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/portugal-vs-uzbekistan-predictions-tips/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No previous meetings between these teams.
+No price boosts for this event.
+Bet Builder is not available yet.
+Betting markets are not available yet.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DR Congo at the World Cup 2026: Team Guide &amp; 26-Man Squad</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/congo-dr-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A team profile of DR Congo (Leopards), back at the FIFA World Cup after 52 years: 46th in the FIFA ranking, 2nd appearance (as Zaire in 1974), Sebasti</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colombia at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/colombia-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A team profile of Colombia (Los Cafeteros) at the FIFA World Cup 2026: 13th in the FIFA ranking, 7th appearance, best result the 2014 quarter-finals, </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6 days ago</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
+Get the latest World Cup Group A betting odds </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>西班牙若头名出线将遇J组第二，若小组第二可能首轮碰阿根廷</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-22 08:38</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/article/5956424</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>美加墨世界杯小组赛两轮过后，在H组，西班牙两战积4分，乌拉圭与佛得角积2分，沙特积1分。最后一轮比赛，西班牙将与乌拉圭直接对话。
+对于H组来说，小组第一和小组第二出线后的形势可能有着天壤之别。 H1将在1/16决赛碰J2， 也就是阿根廷、奥地利所在小组的第二名，而H2将在1/16决赛碰J1，从目前</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Uzbekistan at the World Cup 2026: Team Guide — History, Style, Players &amp; Group K</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>kickoff</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://kickoff.guide/blog/uzbekistan-world-cup-2026-guide</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A team profile of Uzbekistan, who reached a first-ever FIFA World Cup: 50th in the FIFA ranking, coached by Italy's World Cup-winning captain Fabio Ca</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
